--- a/PTBR/Lang/PTBR/Data/god_talk.xlsx
+++ b/PTBR/Lang/PTBR/Data/god_talk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isy\Documents\GitHub\elin-portugues-brasileiro\Traduzido\PTBR\Lang\PTBR\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Users\ysi\Documents\GitHub\elin-portugues-brasileiro\PTBR\Lang\PTBR\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8764B7E0-3F46-4738-8370-E953FAC71565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17948C8-E6F3-4825-8846-FE4662A53CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="217">
   <si>
     <t>id</t>
   </si>
@@ -783,6 +783,39 @@
 Certifique-se de enfrentar um desafio de vez em quando. Oponentes mais fracos ficam entediantes rapidamente.
 A estagnação eventualmente leva à deterioração. O que seria da vida sem um pouco de estimulação?
 Você faz questão de seguir seu próprio caminho. Nada mais divertido para mim do que isso.</t>
+  </si>
+  <si>
+    <t>wedding</t>
+  </si>
+  <si>
+    <t>Que instituição tola. Muito bem, vou celebrá-la só por hoje.</t>
+  </si>
+  <si>
+    <t>Prender-se assim? Que ridículo, gatinho.</t>
+  </si>
+  <si>
+    <t>Em meu nome, concedo minha bênção a vocês dois.</t>
+  </si>
+  <si>
+    <t>Sejam felizes! Felizes!</t>
+  </si>
+  <si>
+    <t>Muahahahahaha!!!</t>
+  </si>
+  <si>
+    <t>N-não é que eu esteja com ciúmes nem nada. ...idiota... parabéns…</t>
+  </si>
+  <si>
+    <t>Nunca se soltem... nunca…</t>
+  </si>
+  <si>
+    <t>Vocês têm minha bênção. Vou me abster de travessuras — só por hoje.</t>
+  </si>
+  <si>
+    <t>Oh minha nossa, que delícia! Parabéns.</t>
+  </si>
+  <si>
+    <t>Deixo meus parabéns. Uma conquista admirável para a sua raça.</t>
   </si>
 </sst>
 </file>
@@ -840,7 +873,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -863,6 +896,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -1161,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -2048,6 +2083,50 @@
       </c>
       <c r="N21"/>
     </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="M22" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
